--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-PAR-Create-Operation-Input.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-PAR-Create-Operation-Input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="223">
   <si>
     <t>Property</t>
   </si>
@@ -383,6 +383,10 @@
     <t>closed</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
   </si>
@@ -423,6 +427,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -462,6 +476,9 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -475,24 +492,31 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
+    <t>ele-1
+inv-1</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
     <t xml:space="preserve">inv-1
 </t>
   </si>
   <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -548,16 +572,6 @@
   </si>
   <si>
     <t>Parameters.parameter.value[x].extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Parameters.parameter:workflowType.value[x].system</t>
@@ -1802,24 +1816,24 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1842,13 +1856,13 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1899,7 +1913,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -1922,14 +1936,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1948,16 +1962,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1995,19 +2009,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2019,7 +2033,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2030,14 +2044,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2056,19 +2070,19 @@
         <v>86</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2117,7 +2131,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2129,21 +2143,21 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2166,15 +2180,17 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2223,7 +2239,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>85</v>
@@ -2246,10 +2262,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2272,13 +2288,13 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2329,7 +2345,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2338,7 +2354,7 @@
         <v>85</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>97</v>
@@ -2347,15 +2363,15 @@
         <v>76</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2378,16 +2394,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2437,7 +2453,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2446,7 +2462,7 @@
         <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>76</v>
@@ -2455,15 +2471,15 @@
         <v>76</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>76</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2489,13 +2505,13 @@
         <v>76</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2545,7 +2561,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2557,7 +2573,7 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>76</v>
@@ -2568,13 +2584,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>113</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>76</v>
@@ -2662,24 +2678,24 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2702,13 +2718,13 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2759,7 +2775,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2782,14 +2798,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2808,16 +2824,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2855,19 +2871,19 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -2879,7 +2895,7 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>76</v>
@@ -2890,14 +2906,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -2916,19 +2932,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -2977,7 +2993,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -2989,21 +3005,21 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3026,15 +3042,17 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3044,7 +3062,7 @@
         <v>76</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>76</v>
@@ -3083,7 +3101,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3106,10 +3124,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3132,13 +3150,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3165,11 +3183,11 @@
         <v>76</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>76</v>
@@ -3187,7 +3205,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3196,7 +3214,7 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>97</v>
@@ -3205,15 +3223,15 @@
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3236,13 +3254,13 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3293,7 +3311,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3316,14 +3334,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3342,16 +3360,16 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3389,19 +3407,19 @@
         <v>76</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3413,7 +3431,7 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -3424,10 +3442,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3453,16 +3471,16 @@
         <v>99</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -3511,7 +3529,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3526,18 +3544,18 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3560,16 +3578,16 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3619,7 +3637,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3634,18 +3652,18 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3671,14 +3689,14 @@
         <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -3727,7 +3745,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3742,18 +3760,18 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3776,17 +3794,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -3835,7 +3855,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -3850,18 +3870,18 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3884,19 +3904,19 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -3945,7 +3965,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -3960,18 +3980,18 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3994,16 +4014,16 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4053,7 +4073,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4062,7 +4082,7 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>76</v>
@@ -4071,15 +4091,15 @@
         <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>76</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4105,13 +4125,13 @@
         <v>76</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4161,7 +4181,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4173,7 +4193,7 @@
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>

--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-PAR-Create-Operation-Input.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-PAR-Create-Operation-Input.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2582,7 +2582,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>164</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>76</v>
